--- a/InputData/trans/BESP/BAU EV Subsidy Perc.xlsx
+++ b/InputData/trans/BESP/BAU EV Subsidy Perc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\State Models\eps-virginia\InputData\trans\BESP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89984FA-D642-42E4-985D-F25C4158D428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DA0B47-DD59-41B3-9D1A-5BD692F885E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="59145" yWindow="960" windowWidth="21825" windowHeight="15060" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId8"/>
+    <pivotCache cacheId="7" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="285">
   <si>
     <t>BESP BAU EV Subsidy Percentage</t>
   </si>
@@ -892,6 +892,9 @@
   </si>
   <si>
     <t>which models will apply under the requirements.</t>
+  </si>
+  <si>
+    <t>Inflation Adjustment (2020 to 2012 USD)</t>
   </si>
 </sst>
 </file>
@@ -905,11 +908,18 @@
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1163,38 +1173,39 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="38" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" pivotButton="1" applyBorder="1"/>
@@ -1210,22 +1221,22 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="6" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1236,9 +1247,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 6" xfId="1" xr:uid="{C05365EF-9BA3-4120-B0B0-32BE67C6FF73}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1283,7 +1296,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Daniel O'Brien" refreshedDate="44965.643362268522" refreshedVersion="8" recordCount="45" xr:uid="{00000000-000A-0000-FFFF-FFFF03000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Daniel O'Brien" refreshedDate="44965.87491273148" refreshedVersion="8" recordCount="45" xr:uid="{00000000-000A-0000-FFFF-FFFF03000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:P47" sheet="2019 Sales"/>
   </cacheSource>
@@ -2180,127 +2193,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="BAU" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="8" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A22:B41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField name="Mfg" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
-      <items count="19">
-        <item x="10"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="15"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="11"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="14"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="Type" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="2019 U.S. EV SALES" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="JAN" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="FEB" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="MAR" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="APR" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="MAY" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="JUN" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="JUL" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="AUG" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="SEP" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="OCT" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="NOV" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="DEC" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField name="TOTAL" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of TOTAL" fld="15" showDataAs="percentOfCol" baseField="0" numFmtId="10"/>
-  </dataFields>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="BAU 2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="8" rowGrandTotals="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="BAU 2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="8" rowGrandTotals="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="G22:J41" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField name="Mfg" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
@@ -2419,6 +2312,126 @@
     <dataField name="Sum of JAN" fld="3" baseField="0"/>
     <dataField name="Sum of FEB" fld="4" baseField="0"/>
     <dataField name="Sum of MAR" fld="5" baseField="0"/>
+  </dataFields>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="BAU" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="8" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A22:B41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField name="Mfg" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
+      <items count="19">
+        <item x="10"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Type" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="2019 U.S. EV SALES" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="JAN" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="FEB" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="MAR" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="APR" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="MAY" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="JUN" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="JUL" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="AUG" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="SEP" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="OCT" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="NOV" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="DEC" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="TOTAL" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of TOTAL" fld="15" showDataAs="percentOfCol" baseField="0" numFmtId="10"/>
   </dataFields>
   <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -3117,7 +3130,12 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="4"/>
+      <c r="A45" s="55">
+        <v>0.88711067149387013</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>284</v>
+      </c>
       <c r="F45" s="5" t="s">
         <v>114</v>
       </c>
@@ -21777,142 +21795,142 @@
       </c>
       <c r="B2" s="38">
         <f>C2</f>
-        <v>2745.8606136031603</v>
+        <v>2435.88225276207</v>
       </c>
       <c r="C2" s="38">
         <f>D2</f>
-        <v>2745.8606136031603</v>
+        <v>2435.88225276207</v>
       </c>
       <c r="D2" s="38">
         <f>E2</f>
-        <v>2745.8606136031603</v>
+        <v>2435.88225276207</v>
       </c>
       <c r="E2" s="39">
-        <f>Data!A33</f>
-        <v>2745.8606136031603</v>
+        <f>Data!A33*About!$A45</f>
+        <v>2435.88225276207</v>
       </c>
       <c r="F2" s="39">
-        <f>Data!B33</f>
-        <v>2745.8606136031599</v>
+        <f>Data!B33*About!$A45</f>
+        <v>2435.8822527620696</v>
       </c>
       <c r="G2" s="39">
-        <f>Data!C33</f>
-        <v>2745.8606136031603</v>
+        <f>Data!C33*About!$A45</f>
+        <v>2435.88225276207</v>
       </c>
       <c r="H2" s="39">
-        <f>Data!D33</f>
-        <v>1913.0458308533109</v>
+        <f>Data!D33*About!$A45</f>
+        <v>1697.0833716068294</v>
       </c>
       <c r="I2" s="39">
-        <f>Data!E33</f>
+        <f>Data!E33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="J2" s="39">
-        <f>Data!F33</f>
+        <f>Data!F33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="K2" s="39">
-        <f>Data!G33</f>
+        <f>Data!G33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="L2" s="39">
-        <f>Data!H33</f>
+        <f>Data!H33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="M2" s="39">
-        <f>Data!I33</f>
+        <f>Data!I33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="N2" s="39">
-        <f>Data!J33</f>
+        <f>Data!J33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="O2" s="39">
-        <f>Data!K33</f>
+        <f>Data!K33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="P2" s="39">
-        <f>Data!L33</f>
+        <f>Data!L33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="Q2" s="39">
-        <f>Data!M33</f>
+        <f>Data!M33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="R2" s="39">
-        <f>Data!N33</f>
+        <f>Data!N33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="S2" s="39">
-        <f>Data!O33</f>
+        <f>Data!O33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="T2" s="39">
-        <f>Data!P33</f>
+        <f>Data!P33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="U2" s="39">
-        <f>Data!Q33</f>
+        <f>Data!Q33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="V2" s="39">
-        <f>Data!R33</f>
+        <f>Data!R33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="W2" s="39">
-        <f>Data!S33</f>
+        <f>Data!S33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="X2" s="39">
-        <f>Data!T33</f>
+        <f>Data!T33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="Y2" s="39">
-        <f>Data!U33</f>
+        <f>Data!U33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="Z2" s="39">
-        <f>Data!V33</f>
+        <f>Data!V33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="AA2" s="39">
-        <f>Data!W33</f>
+        <f>Data!W33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="AB2" s="39">
-        <f>Data!X33</f>
+        <f>Data!X33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="AC2" s="39">
-        <f>Data!Y33</f>
+        <f>Data!Y33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="AD2" s="39">
-        <f>Data!Z33</f>
+        <f>Data!Z33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="AE2" s="39">
-        <f>Data!AA33</f>
+        <f>Data!AA33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="AF2" s="39">
-        <f>Data!AB33</f>
+        <f>Data!AB33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="AG2" s="39">
-        <f>Data!AC33</f>
+        <f>Data!AC33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="AH2" s="39">
-        <f>Data!AD33</f>
+        <f>Data!AD33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="AI2" s="39">
-        <f>Data!AE33</f>
+        <f>Data!AE33*About!$A45</f>
         <v>0</v>
       </c>
       <c r="AJ2" s="39">
-        <f>Data!AF33</f>
+        <f>Data!AF33*About!$A45</f>
         <v>0</v>
       </c>
     </row>
